--- a/data/all_datasets/REDD/REDD_House6_stats/2026-04-17.xlsx
+++ b/data/all_datasets/REDD/REDD_House6_stats/2026-04-17.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.7393453828003</v>
+        <v>15.93389939432857</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7247049936742326</v>
+        <v>0.7813283539623944</v>
       </c>
     </row>
     <row r="3">
@@ -773,7 +773,7 @@
         <v>1.556725173665137</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09610131317768586</v>
+        <v>0.07633495652323076</v>
       </c>
     </row>
     <row r="4">
@@ -786,7 +786,7 @@
         <v>1.251759082991777</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07727484188771919</v>
+        <v>0.06138076058265804</v>
       </c>
     </row>
     <row r="5">
@@ -799,7 +799,7 @@
         <v>0.859412998873273</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05305414157287885</v>
+        <v>0.04214183403357901</v>
       </c>
     </row>
     <row r="6">
@@ -812,7 +812,7 @@
         <v>0.7915492635745485</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04886470968748352</v>
+        <v>0.03881409489813768</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.7393453828003</v>
+        <v>15.93389939432857</v>
       </c>
     </row>
     <row r="3">
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -972,7 +972,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1012,7 +1012,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1052,7 +1052,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1092,7 +1092,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1172,7 +1172,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1192,7 +1192,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1212,7 +1212,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1272,7 +1272,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1292,7 +1292,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -1352,7 +1352,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -1392,7 +1392,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -1432,7 +1432,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1512,7 +1512,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -1572,7 +1572,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -1612,7 +1612,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -1692,7 +1692,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -1752,7 +1752,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -1892,7 +1892,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -1912,7 +1912,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -1952,7 +1952,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1972,7 +1972,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -2012,7 +2012,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -2032,7 +2032,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -2112,7 +2112,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -2192,7 +2192,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -2232,7 +2232,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -2272,7 +2272,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -2392,7 +2392,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -2552,7 +2552,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -2572,7 +2572,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -2592,7 +2592,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -2672,7 +2672,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -2732,7 +2732,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -2832,7 +2832,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -2852,7 +2852,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -2932,7 +2932,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -2952,7 +2952,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -2992,7 +2992,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -3012,7 +3012,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -3032,7 +3032,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -3052,7 +3052,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -3152,7 +3152,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -3172,7 +3172,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -3212,7 +3212,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -3232,7 +3232,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -3272,7 +3272,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -3292,7 +3292,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -3352,7 +3352,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -3392,7 +3392,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -3412,7 +3412,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -3432,7 +3432,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -3492,7 +3492,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -3532,7 +3532,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -3592,7 +3592,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -3612,7 +3612,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -3652,7 +3652,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -3692,7 +3692,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -3712,7 +3712,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -3752,7 +3752,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -3812,7 +3812,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -3852,7 +3852,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -3912,7 +3912,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -3992,7 +3992,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -4012,7 +4012,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -4032,7 +4032,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -4092,7 +4092,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -4112,7 +4112,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -4132,7 +4132,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -4252,7 +4252,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -4272,7 +4272,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -4292,7 +4292,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -4332,7 +4332,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -4352,7 +4352,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -4372,7 +4372,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -4432,7 +4432,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -4452,7 +4452,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -4472,7 +4472,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -4512,7 +4512,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -4532,7 +4532,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -4552,7 +4552,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -4572,7 +4572,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -4592,7 +4592,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -4612,7 +4612,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -4652,7 +4652,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -4672,7 +4672,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -4692,7 +4692,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -4712,7 +4712,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -4732,7 +4732,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -4772,7 +4772,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -4812,7 +4812,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -4832,7 +4832,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -4852,7 +4852,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -4872,7 +4872,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -4892,7 +4892,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -4912,7 +4912,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
@@ -4952,7 +4952,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
@@ -4972,7 +4972,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
@@ -4992,7 +4992,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
@@ -5092,7 +5092,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
@@ -5112,7 +5112,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
@@ -5132,7 +5132,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
@@ -5172,7 +5172,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
@@ -5192,7 +5192,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
@@ -5232,7 +5232,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
@@ -5252,7 +5252,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
@@ -5272,7 +5272,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
@@ -5292,7 +5292,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
@@ -5312,7 +5312,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
@@ -5352,7 +5352,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
@@ -5372,7 +5372,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C223" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
@@ -5412,7 +5412,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
@@ -5432,7 +5432,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
@@ -5452,7 +5452,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
@@ -5472,7 +5472,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
@@ -5512,7 +5512,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -5532,7 +5532,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
@@ -5592,7 +5592,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
@@ -5672,7 +5672,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
@@ -5692,7 +5692,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
@@ -5712,7 +5712,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -5732,7 +5732,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C241" t="n">
         <v>0</v>
@@ -5752,7 +5752,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
@@ -5812,7 +5812,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C245" t="n">
         <v>0</v>
@@ -5832,7 +5832,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C247" t="n">
         <v>0</v>
@@ -5872,7 +5872,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -5912,7 +5912,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
@@ -5932,7 +5932,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C251" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C252" t="n">
         <v>0</v>
@@ -5972,7 +5972,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
@@ -5992,7 +5992,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
@@ -6012,7 +6012,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
@@ -6032,7 +6032,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
@@ -6052,7 +6052,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C259" t="n">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C261" t="n">
         <v>0</v>
@@ -6152,7 +6152,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C262" t="n">
         <v>0</v>
@@ -6172,7 +6172,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C263" t="n">
         <v>0</v>
@@ -6192,7 +6192,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C264" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C265" t="n">
         <v>0</v>
@@ -6232,7 +6232,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C266" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C267" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C268" t="n">
         <v>0</v>
@@ -6292,7 +6292,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C269" t="n">
         <v>0</v>
@@ -6312,7 +6312,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C270" t="n">
         <v>0</v>
@@ -6332,7 +6332,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C271" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C272" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C273" t="n">
         <v>0</v>
@@ -6392,7 +6392,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C274" t="n">
         <v>0</v>
@@ -6412,7 +6412,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C275" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C276" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C277" t="n">
         <v>0</v>
@@ -6472,7 +6472,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C278" t="n">
         <v>0</v>
@@ -6492,7 +6492,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C279" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C280" t="n">
         <v>0</v>
@@ -6532,7 +6532,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C281" t="n">
         <v>0</v>
@@ -6552,7 +6552,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C282" t="n">
         <v>0</v>
@@ -6572,7 +6572,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C283" t="n">
         <v>0</v>
@@ -6592,7 +6592,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C284" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C285" t="n">
         <v>0</v>
@@ -6632,7 +6632,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C286" t="n">
         <v>0</v>
@@ -6652,7 +6652,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C287" t="n">
         <v>0</v>
@@ -6672,7 +6672,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C288" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C289" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C290" t="n">
         <v>0</v>
@@ -6732,7 +6732,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C291" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C292" t="n">
         <v>0</v>
@@ -6772,7 +6772,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C293" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C294" t="n">
         <v>0</v>
@@ -6812,7 +6812,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C295" t="n">
         <v>0</v>
@@ -6832,7 +6832,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C296" t="n">
         <v>0</v>
@@ -6852,7 +6852,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C297" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C298" t="n">
         <v>0</v>
@@ -6892,7 +6892,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C299" t="n">
         <v>0</v>
@@ -6912,7 +6912,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C300" t="n">
         <v>0</v>
@@ -6932,7 +6932,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C301" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C302" t="n">
         <v>0</v>
@@ -6972,7 +6972,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C303" t="n">
         <v>0</v>
@@ -6992,7 +6992,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C304" t="n">
         <v>0</v>
@@ -7012,7 +7012,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C305" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C306" t="n">
         <v>0</v>
@@ -7052,7 +7052,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C307" t="n">
         <v>0</v>
@@ -7072,7 +7072,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C308" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C309" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C310" t="n">
         <v>0</v>
@@ -7132,7 +7132,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C311" t="n">
         <v>0</v>
@@ -7152,7 +7152,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C312" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C313" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C314" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C315" t="n">
         <v>0</v>
@@ -7232,7 +7232,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C316" t="n">
         <v>0</v>
@@ -7252,7 +7252,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C317" t="n">
         <v>0</v>
@@ -7272,7 +7272,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C318" t="n">
         <v>0</v>
@@ -7292,7 +7292,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C319" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C320" t="n">
         <v>0</v>
@@ -7332,7 +7332,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C321" t="n">
         <v>0</v>
@@ -7352,7 +7352,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C322" t="n">
         <v>0</v>
@@ -7372,7 +7372,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C323" t="n">
         <v>0</v>
@@ -7392,7 +7392,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C324" t="n">
         <v>0</v>
@@ -7412,7 +7412,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C325" t="n">
         <v>0</v>
@@ -7432,7 +7432,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C326" t="n">
         <v>0</v>
@@ -7452,7 +7452,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C327" t="n">
         <v>0</v>
@@ -7472,7 +7472,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C328" t="n">
         <v>0</v>
@@ -7492,7 +7492,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C329" t="n">
         <v>0</v>
@@ -7512,7 +7512,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C330" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C331" t="n">
         <v>0</v>
@@ -7552,7 +7552,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C332" t="n">
         <v>103.8359287054302</v>
@@ -7572,7 +7572,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C333" t="n">
         <v>103.8359287054302</v>
@@ -7592,7 +7592,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C334" t="n">
         <v>103.8359287054302</v>
@@ -7612,7 +7612,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C335" t="n">
         <v>103.8359287054302</v>
@@ -7632,7 +7632,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C336" t="n">
         <v>103.8359287054302</v>
@@ -7652,7 +7652,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C337" t="n">
         <v>103.8359287054302</v>
@@ -7672,7 +7672,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C338" t="n">
         <v>103.8359287054302</v>
@@ -7692,7 +7692,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C339" t="n">
         <v>103.8359287054302</v>
@@ -7712,7 +7712,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C340" t="n">
         <v>103.8359287054302</v>
@@ -7732,7 +7732,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C341" t="n">
         <v>103.8359287054302</v>
@@ -7752,7 +7752,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C342" t="n">
         <v>103.8359287054302</v>
@@ -7772,7 +7772,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C343" t="n">
         <v>103.8359287054302</v>
@@ -7792,7 +7792,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C344" t="n">
         <v>103.8359287054302</v>
@@ -7812,7 +7812,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C345" t="n">
         <v>103.8359287054302</v>
@@ -7832,7 +7832,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C346" t="n">
         <v>103.8359287054302</v>
@@ -7852,7 +7852,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C347" t="n">
         <v>103.8359287054302</v>
@@ -7872,7 +7872,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C348" t="n">
         <v>103.8359287054302</v>
@@ -7892,7 +7892,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C349" t="n">
         <v>103.8359287054302</v>
@@ -7912,7 +7912,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C350" t="n">
         <v>103.8359287054302</v>
@@ -7932,7 +7932,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C351" t="n">
         <v>103.8359287054302</v>
@@ -7952,7 +7952,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C352" t="n">
         <v>103.8359287054302</v>
@@ -7972,7 +7972,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C353" t="n">
         <v>103.8359287054302</v>
@@ -7992,7 +7992,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C354" t="n">
         <v>103.8359287054302</v>
@@ -8012,7 +8012,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C355" t="n">
         <v>103.8359287054302</v>
@@ -8032,7 +8032,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C356" t="n">
         <v>103.8359287054302</v>
@@ -8052,7 +8052,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C357" t="n">
         <v>103.8359287054302</v>
@@ -8072,7 +8072,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C358" t="n">
         <v>103.8359287054302</v>
@@ -8092,7 +8092,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C359" t="n">
         <v>103.8359287054302</v>
@@ -8112,7 +8112,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C360" t="n">
         <v>103.8359287054302</v>
@@ -8132,7 +8132,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C361" t="n">
         <v>103.8359287054302</v>
@@ -8152,7 +8152,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C362" t="n">
         <v>103.8359287054302</v>
@@ -8172,7 +8172,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C363" t="n">
         <v>103.8359287054302</v>
@@ -8192,7 +8192,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C364" t="n">
         <v>103.8359287054302</v>
@@ -8212,7 +8212,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C365" t="n">
         <v>103.8359287054302</v>
@@ -8232,7 +8232,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C366" t="n">
         <v>103.8359287054302</v>
@@ -8252,7 +8252,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C367" t="n">
         <v>103.8359287054302</v>
@@ -8272,7 +8272,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C368" t="n">
         <v>103.8359287054302</v>
@@ -8292,7 +8292,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C369" t="n">
         <v>103.8359287054302</v>
@@ -8312,7 +8312,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C370" t="n">
         <v>103.8359287054302</v>
@@ -8332,7 +8332,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C371" t="n">
         <v>103.8359287054302</v>
@@ -8352,7 +8352,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C372" t="n">
         <v>103.8359287054302</v>
@@ -8372,7 +8372,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C373" t="n">
         <v>103.8359287054302</v>
@@ -8392,7 +8392,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C374" t="n">
         <v>103.8359287054302</v>
@@ -8412,7 +8412,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C375" t="n">
         <v>103.8359287054302</v>
@@ -8432,7 +8432,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C376" t="n">
         <v>103.8359287054302</v>
@@ -8452,7 +8452,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C377" t="n">
         <v>103.8359287054302</v>
@@ -8472,7 +8472,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C378" t="n">
         <v>103.8359287054302</v>
@@ -8492,7 +8492,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C379" t="n">
         <v>103.8359287054302</v>
@@ -8512,7 +8512,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C380" t="n">
         <v>103.8359287054302</v>
@@ -8532,7 +8532,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C381" t="n">
         <v>103.8359287054302</v>
@@ -8552,7 +8552,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C382" t="n">
         <v>103.8359287054302</v>
@@ -8572,7 +8572,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C383" t="n">
         <v>103.8359287054302</v>
@@ -8592,7 +8592,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C384" t="n">
         <v>103.8359287054302</v>
@@ -8612,7 +8612,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C385" t="n">
         <v>103.8359287054302</v>
@@ -8632,7 +8632,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C386" t="n">
         <v>103.8359287054302</v>
@@ -8652,7 +8652,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C387" t="n">
         <v>103.8359287054302</v>
@@ -8672,7 +8672,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C388" t="n">
         <v>103.8359287054302</v>
@@ -8692,7 +8692,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C389" t="n">
         <v>103.8359287054302</v>
@@ -8712,7 +8712,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C390" t="n">
         <v>103.8359287054302</v>
@@ -8732,7 +8732,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C391" t="n">
         <v>103.8359287054302</v>
@@ -8752,7 +8752,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C392" t="n">
         <v>103.8359287054302</v>
@@ -8772,7 +8772,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C393" t="n">
         <v>103.8359287054302</v>
@@ -8792,7 +8792,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C394" t="n">
         <v>103.8359287054302</v>
@@ -8812,7 +8812,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C395" t="n">
         <v>103.8359287054302</v>
@@ -8832,7 +8832,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C396" t="n">
         <v>103.8359287054302</v>
@@ -8852,7 +8852,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C397" t="n">
         <v>103.8359287054302</v>
@@ -8872,7 +8872,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C398" t="n">
         <v>103.8359287054302</v>
@@ -8892,7 +8892,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C399" t="n">
         <v>103.8359287054302</v>
@@ -8912,7 +8912,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C400" t="n">
         <v>103.8359287054302</v>
@@ -8932,7 +8932,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C401" t="n">
         <v>103.8359287054302</v>
@@ -8952,7 +8952,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C402" t="n">
         <v>103.8359287054302</v>
@@ -8972,7 +8972,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C403" t="n">
         <v>103.8359287054302</v>
@@ -8992,7 +8992,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C404" t="n">
         <v>103.8359287054302</v>
@@ -9012,7 +9012,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C405" t="n">
         <v>103.8359287054302</v>
@@ -9032,7 +9032,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C406" t="n">
         <v>103.8359287054302</v>
@@ -9052,7 +9052,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C407" t="n">
         <v>103.8359287054302</v>
@@ -9072,7 +9072,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C408" t="n">
         <v>103.8359287054302</v>
@@ -9092,7 +9092,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C409" t="n">
         <v>103.8359287054302</v>
@@ -9112,7 +9112,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C410" t="n">
         <v>103.8359287054302</v>
@@ -9132,7 +9132,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C411" t="n">
         <v>103.8359287054302</v>
@@ -9152,7 +9152,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C412" t="n">
         <v>103.8359287054302</v>
@@ -9172,7 +9172,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C413" t="n">
         <v>103.8359287054302</v>
@@ -9192,7 +9192,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C414" t="n">
         <v>103.8359287054302</v>
@@ -9212,7 +9212,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C415" t="n">
         <v>103.8359287054302</v>
@@ -9232,7 +9232,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C416" t="n">
         <v>103.8359287054302</v>
@@ -9252,7 +9252,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C417" t="n">
         <v>103.8359287054302</v>
@@ -9272,7 +9272,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C418" t="n">
         <v>103.8359287054302</v>
@@ -9292,7 +9292,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C419" t="n">
         <v>103.8359287054302</v>
@@ -9312,7 +9312,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C420" t="n">
         <v>103.8359287054302</v>
@@ -9332,7 +9332,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C421" t="n">
         <v>103.8359287054302</v>
@@ -9352,7 +9352,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C422" t="n">
         <v>103.8359287054302</v>
@@ -9372,7 +9372,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C423" t="n">
         <v>103.8359287054302</v>
@@ -9392,7 +9392,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C424" t="n">
         <v>103.8359287054302</v>
@@ -9412,7 +9412,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C425" t="n">
         <v>103.8359287054302</v>
@@ -9432,7 +9432,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C426" t="n">
         <v>103.8359287054302</v>
@@ -9452,7 +9452,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C427" t="n">
         <v>103.8359287054302</v>
@@ -9472,7 +9472,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C428" t="n">
         <v>103.8359287054302</v>
@@ -9492,7 +9492,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C429" t="n">
         <v>103.8359287054302</v>
@@ -9512,7 +9512,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C430" t="n">
         <v>103.8359287054302</v>
@@ -9532,7 +9532,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C431" t="n">
         <v>103.8359287054302</v>
@@ -9552,7 +9552,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C432" t="n">
         <v>103.8359287054302</v>
@@ -9572,7 +9572,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C433" t="n">
         <v>103.8359287054302</v>
@@ -9592,7 +9592,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C434" t="n">
         <v>103.8359287054302</v>
@@ -9612,7 +9612,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C435" t="n">
         <v>103.8359287054302</v>
@@ -9632,7 +9632,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C436" t="n">
         <v>103.8359287054302</v>
@@ -9652,7 +9652,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C437" t="n">
         <v>103.8359287054302</v>
@@ -9672,7 +9672,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C438" t="n">
         <v>103.8359287054302</v>
@@ -9692,7 +9692,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C439" t="n">
         <v>103.8359287054302</v>
@@ -9712,7 +9712,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C440" t="n">
         <v>103.8359287054302</v>
@@ -9732,7 +9732,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C441" t="n">
         <v>103.8359287054302</v>
@@ -9752,7 +9752,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C442" t="n">
         <v>103.8359287054302</v>
@@ -9772,7 +9772,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C443" t="n">
         <v>103.8359287054302</v>
@@ -9792,7 +9792,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C444" t="n">
         <v>103.8359287054302</v>
@@ -9812,7 +9812,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C445" t="n">
         <v>103.8359287054302</v>
@@ -9832,7 +9832,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C446" t="n">
         <v>103.8359287054302</v>
@@ -9852,7 +9852,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C447" t="n">
         <v>103.8359287054302</v>
@@ -9872,7 +9872,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C448" t="n">
         <v>103.8359287054302</v>
@@ -9892,7 +9892,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C449" t="n">
         <v>103.8359287054302</v>
@@ -9912,7 +9912,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C450" t="n">
         <v>103.8359287054302</v>
@@ -9932,7 +9932,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C451" t="n">
         <v>103.8359287054302</v>
@@ -9952,7 +9952,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C452" t="n">
         <v>103.8359287054302</v>
@@ -9972,7 +9972,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C453" t="n">
         <v>103.8359287054302</v>
@@ -9992,7 +9992,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C454" t="n">
         <v>103.8359287054302</v>
@@ -10012,7 +10012,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C455" t="n">
         <v>103.8359287054302</v>
@@ -10032,7 +10032,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C456" t="n">
         <v>103.8359287054302</v>
@@ -10052,7 +10052,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C457" t="n">
         <v>103.8359287054302</v>
@@ -10072,7 +10072,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C458" t="n">
         <v>103.8359287054302</v>
@@ -10092,7 +10092,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C459" t="n">
         <v>103.8359287054302</v>
@@ -10112,7 +10112,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C460" t="n">
         <v>103.8359287054302</v>
@@ -10132,7 +10132,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C461" t="n">
         <v>103.8359287054302</v>
@@ -10152,7 +10152,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C462" t="n">
         <v>103.8359287054302</v>
@@ -10172,7 +10172,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C463" t="n">
         <v>103.8359287054302</v>
@@ -10192,7 +10192,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C464" t="n">
         <v>103.8359287054302</v>
@@ -10212,7 +10212,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C465" t="n">
         <v>103.8359287054302</v>
@@ -24652,7 +24652,7 @@
         <v>1185</v>
       </c>
       <c r="B1187" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1187" t="n">
         <v>103.8359287054302</v>
@@ -24672,7 +24672,7 @@
         <v>1186</v>
       </c>
       <c r="B1188" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1188" t="n">
         <v>103.8359287054302</v>
@@ -24692,7 +24692,7 @@
         <v>1187</v>
       </c>
       <c r="B1189" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1189" t="n">
         <v>103.8359287054302</v>
@@ -24712,7 +24712,7 @@
         <v>1188</v>
       </c>
       <c r="B1190" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1190" t="n">
         <v>103.8359287054302</v>
@@ -24732,7 +24732,7 @@
         <v>1189</v>
       </c>
       <c r="B1191" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1191" t="n">
         <v>103.8359287054302</v>
@@ -24752,7 +24752,7 @@
         <v>1190</v>
       </c>
       <c r="B1192" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1192" t="n">
         <v>103.8359287054302</v>
@@ -24772,7 +24772,7 @@
         <v>1191</v>
       </c>
       <c r="B1193" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1193" t="n">
         <v>103.8359287054302</v>
@@ -24792,7 +24792,7 @@
         <v>1192</v>
       </c>
       <c r="B1194" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1194" t="n">
         <v>103.8359287054302</v>
@@ -24812,7 +24812,7 @@
         <v>1193</v>
       </c>
       <c r="B1195" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1195" t="n">
         <v>103.8359287054302</v>
@@ -24832,7 +24832,7 @@
         <v>1194</v>
       </c>
       <c r="B1196" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1196" t="n">
         <v>103.8359287054302</v>
@@ -24852,7 +24852,7 @@
         <v>1195</v>
       </c>
       <c r="B1197" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1197" t="n">
         <v>103.8359287054302</v>
@@ -24872,7 +24872,7 @@
         <v>1196</v>
       </c>
       <c r="B1198" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1198" t="n">
         <v>103.8359287054302</v>
@@ -24892,7 +24892,7 @@
         <v>1197</v>
       </c>
       <c r="B1199" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1199" t="n">
         <v>103.8359287054302</v>
@@ -24912,7 +24912,7 @@
         <v>1198</v>
       </c>
       <c r="B1200" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1200" t="n">
         <v>103.8359287054302</v>
@@ -24932,7 +24932,7 @@
         <v>1199</v>
       </c>
       <c r="B1201" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1201" t="n">
         <v>103.8359287054302</v>
@@ -24952,7 +24952,7 @@
         <v>1200</v>
       </c>
       <c r="B1202" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1202" t="n">
         <v>0</v>
@@ -24972,7 +24972,7 @@
         <v>1201</v>
       </c>
       <c r="B1203" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1203" t="n">
         <v>0</v>
@@ -24992,7 +24992,7 @@
         <v>1202</v>
       </c>
       <c r="B1204" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1204" t="n">
         <v>0</v>
@@ -25012,7 +25012,7 @@
         <v>1203</v>
       </c>
       <c r="B1205" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1205" t="n">
         <v>0</v>
@@ -25032,7 +25032,7 @@
         <v>1204</v>
       </c>
       <c r="B1206" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1206" t="n">
         <v>0</v>
@@ -25052,7 +25052,7 @@
         <v>1205</v>
       </c>
       <c r="B1207" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1207" t="n">
         <v>0</v>
@@ -25072,7 +25072,7 @@
         <v>1206</v>
       </c>
       <c r="B1208" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1208" t="n">
         <v>0</v>
@@ -25092,7 +25092,7 @@
         <v>1207</v>
       </c>
       <c r="B1209" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1209" t="n">
         <v>0</v>
@@ -25112,7 +25112,7 @@
         <v>1208</v>
       </c>
       <c r="B1210" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1210" t="n">
         <v>0</v>
@@ -25132,7 +25132,7 @@
         <v>1209</v>
       </c>
       <c r="B1211" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1211" t="n">
         <v>0</v>
@@ -25152,7 +25152,7 @@
         <v>1210</v>
       </c>
       <c r="B1212" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1212" t="n">
         <v>0</v>
@@ -25172,7 +25172,7 @@
         <v>1211</v>
       </c>
       <c r="B1213" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1213" t="n">
         <v>0</v>
@@ -25192,7 +25192,7 @@
         <v>1212</v>
       </c>
       <c r="B1214" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1214" t="n">
         <v>0</v>
@@ -25212,7 +25212,7 @@
         <v>1213</v>
       </c>
       <c r="B1215" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1215" t="n">
         <v>0</v>
@@ -25232,7 +25232,7 @@
         <v>1214</v>
       </c>
       <c r="B1216" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1216" t="n">
         <v>0</v>
@@ -25252,7 +25252,7 @@
         <v>1215</v>
       </c>
       <c r="B1217" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1217" t="n">
         <v>68.1389432485323</v>
@@ -25272,7 +25272,7 @@
         <v>1216</v>
       </c>
       <c r="B1218" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1218" t="n">
         <v>68.1389432485323</v>
@@ -25292,7 +25292,7 @@
         <v>1217</v>
       </c>
       <c r="B1219" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1219" t="n">
         <v>68.1389432485323</v>
@@ -25312,7 +25312,7 @@
         <v>1218</v>
       </c>
       <c r="B1220" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1220" t="n">
         <v>68.1389432485323</v>
@@ -25332,7 +25332,7 @@
         <v>1219</v>
       </c>
       <c r="B1221" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1221" t="n">
         <v>68.1389432485323</v>
@@ -25352,7 +25352,7 @@
         <v>1220</v>
       </c>
       <c r="B1222" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1222" t="n">
         <v>68.1389432485323</v>
@@ -25372,7 +25372,7 @@
         <v>1221</v>
       </c>
       <c r="B1223" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1223" t="n">
         <v>68.1389432485323</v>
@@ -25392,7 +25392,7 @@
         <v>1222</v>
       </c>
       <c r="B1224" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1224" t="n">
         <v>68.1389432485323</v>
@@ -25412,7 +25412,7 @@
         <v>1223</v>
       </c>
       <c r="B1225" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1225" t="n">
         <v>68.1389432485323</v>
@@ -25432,7 +25432,7 @@
         <v>1224</v>
       </c>
       <c r="B1226" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1226" t="n">
         <v>68.1389432485323</v>
@@ -25452,7 +25452,7 @@
         <v>1225</v>
       </c>
       <c r="B1227" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1227" t="n">
         <v>68.1389432485323</v>
@@ -25472,7 +25472,7 @@
         <v>1226</v>
       </c>
       <c r="B1228" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1228" t="n">
         <v>68.1389432485323</v>
@@ -25492,7 +25492,7 @@
         <v>1227</v>
       </c>
       <c r="B1229" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1229" t="n">
         <v>68.1389432485323</v>
@@ -25512,7 +25512,7 @@
         <v>1228</v>
       </c>
       <c r="B1230" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1230" t="n">
         <v>68.1389432485323</v>
@@ -25532,7 +25532,7 @@
         <v>1229</v>
       </c>
       <c r="B1231" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1231" t="n">
         <v>68.1389432485323</v>
@@ -25552,7 +25552,7 @@
         <v>1230</v>
       </c>
       <c r="B1232" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1232" t="n">
         <v>68.1389432485323</v>
@@ -25572,7 +25572,7 @@
         <v>1231</v>
       </c>
       <c r="B1233" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1233" t="n">
         <v>68.1389432485323</v>
@@ -25592,7 +25592,7 @@
         <v>1232</v>
       </c>
       <c r="B1234" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1234" t="n">
         <v>68.1389432485323</v>
@@ -25612,7 +25612,7 @@
         <v>1233</v>
       </c>
       <c r="B1235" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1235" t="n">
         <v>68.1389432485323</v>
@@ -25632,7 +25632,7 @@
         <v>1234</v>
       </c>
       <c r="B1236" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1236" t="n">
         <v>68.1389432485323</v>
@@ -25652,7 +25652,7 @@
         <v>1235</v>
       </c>
       <c r="B1237" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1237" t="n">
         <v>68.1389432485323</v>
@@ -25672,7 +25672,7 @@
         <v>1236</v>
       </c>
       <c r="B1238" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1238" t="n">
         <v>68.1389432485323</v>
@@ -25692,7 +25692,7 @@
         <v>1237</v>
       </c>
       <c r="B1239" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1239" t="n">
         <v>68.1389432485323</v>
@@ -25712,7 +25712,7 @@
         <v>1238</v>
       </c>
       <c r="B1240" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1240" t="n">
         <v>68.1389432485323</v>
@@ -25732,7 +25732,7 @@
         <v>1239</v>
       </c>
       <c r="B1241" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1241" t="n">
         <v>68.1389432485323</v>
@@ -25752,7 +25752,7 @@
         <v>1240</v>
       </c>
       <c r="B1242" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1242" t="n">
         <v>68.1389432485323</v>
@@ -25772,7 +25772,7 @@
         <v>1241</v>
       </c>
       <c r="B1243" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1243" t="n">
         <v>68.1389432485323</v>
@@ -25792,7 +25792,7 @@
         <v>1242</v>
       </c>
       <c r="B1244" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1244" t="n">
         <v>68.1389432485323</v>
@@ -25812,7 +25812,7 @@
         <v>1243</v>
       </c>
       <c r="B1245" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1245" t="n">
         <v>68.1389432485323</v>
@@ -25832,7 +25832,7 @@
         <v>1244</v>
       </c>
       <c r="B1246" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C1246" t="n">
         <v>68.1389432485323</v>
@@ -26452,7 +26452,7 @@
         <v>1275</v>
       </c>
       <c r="B1277" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1277" t="n">
         <v>0</v>
@@ -26472,7 +26472,7 @@
         <v>1276</v>
       </c>
       <c r="B1278" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1278" t="n">
         <v>0</v>
@@ -26492,7 +26492,7 @@
         <v>1277</v>
       </c>
       <c r="B1279" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1279" t="n">
         <v>0</v>
@@ -26512,7 +26512,7 @@
         <v>1278</v>
       </c>
       <c r="B1280" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1280" t="n">
         <v>0</v>
@@ -26532,7 +26532,7 @@
         <v>1279</v>
       </c>
       <c r="B1281" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1281" t="n">
         <v>0</v>
@@ -26552,7 +26552,7 @@
         <v>1280</v>
       </c>
       <c r="B1282" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1282" t="n">
         <v>0</v>
@@ -26572,7 +26572,7 @@
         <v>1281</v>
       </c>
       <c r="B1283" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1283" t="n">
         <v>0</v>
@@ -26592,7 +26592,7 @@
         <v>1282</v>
       </c>
       <c r="B1284" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1284" t="n">
         <v>0</v>
@@ -26612,7 +26612,7 @@
         <v>1283</v>
       </c>
       <c r="B1285" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1285" t="n">
         <v>0</v>
@@ -26632,7 +26632,7 @@
         <v>1284</v>
       </c>
       <c r="B1286" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1286" t="n">
         <v>0</v>
@@ -26652,7 +26652,7 @@
         <v>1285</v>
       </c>
       <c r="B1287" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1287" t="n">
         <v>0</v>
@@ -26672,7 +26672,7 @@
         <v>1286</v>
       </c>
       <c r="B1288" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1288" t="n">
         <v>0</v>
@@ -26692,7 +26692,7 @@
         <v>1287</v>
       </c>
       <c r="B1289" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1289" t="n">
         <v>0</v>
@@ -26712,7 +26712,7 @@
         <v>1288</v>
       </c>
       <c r="B1290" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1290" t="n">
         <v>0</v>
@@ -26732,7 +26732,7 @@
         <v>1289</v>
       </c>
       <c r="B1291" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1291" t="n">
         <v>0</v>
@@ -26752,7 +26752,7 @@
         <v>1290</v>
       </c>
       <c r="B1292" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1292" t="n">
         <v>0</v>
@@ -26772,7 +26772,7 @@
         <v>1291</v>
       </c>
       <c r="B1293" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1293" t="n">
         <v>0</v>
@@ -26792,7 +26792,7 @@
         <v>1292</v>
       </c>
       <c r="B1294" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1294" t="n">
         <v>0</v>
@@ -26812,7 +26812,7 @@
         <v>1293</v>
       </c>
       <c r="B1295" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1295" t="n">
         <v>0</v>
@@ -26832,7 +26832,7 @@
         <v>1294</v>
       </c>
       <c r="B1296" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1296" t="n">
         <v>0</v>
@@ -26852,7 +26852,7 @@
         <v>1295</v>
       </c>
       <c r="B1297" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1297" t="n">
         <v>0</v>
@@ -26872,7 +26872,7 @@
         <v>1296</v>
       </c>
       <c r="B1298" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1298" t="n">
         <v>0</v>
@@ -26892,7 +26892,7 @@
         <v>1297</v>
       </c>
       <c r="B1299" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1299" t="n">
         <v>0</v>
@@ -26912,7 +26912,7 @@
         <v>1298</v>
       </c>
       <c r="B1300" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1300" t="n">
         <v>0</v>
@@ -26932,7 +26932,7 @@
         <v>1299</v>
       </c>
       <c r="B1301" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1301" t="n">
         <v>0</v>
@@ -26952,7 +26952,7 @@
         <v>1300</v>
       </c>
       <c r="B1302" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1302" t="n">
         <v>0</v>
@@ -26972,7 +26972,7 @@
         <v>1301</v>
       </c>
       <c r="B1303" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1303" t="n">
         <v>0</v>
@@ -26992,7 +26992,7 @@
         <v>1302</v>
       </c>
       <c r="B1304" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1304" t="n">
         <v>0</v>
@@ -27012,7 +27012,7 @@
         <v>1303</v>
       </c>
       <c r="B1305" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1305" t="n">
         <v>0</v>
@@ -27032,7 +27032,7 @@
         <v>1304</v>
       </c>
       <c r="B1306" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1306" t="n">
         <v>0</v>
@@ -27052,7 +27052,7 @@
         <v>1305</v>
       </c>
       <c r="B1307" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1307" t="n">
         <v>0</v>
@@ -27072,7 +27072,7 @@
         <v>1306</v>
       </c>
       <c r="B1308" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1308" t="n">
         <v>0</v>
@@ -27092,7 +27092,7 @@
         <v>1307</v>
       </c>
       <c r="B1309" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1309" t="n">
         <v>0</v>
@@ -27112,7 +27112,7 @@
         <v>1308</v>
       </c>
       <c r="B1310" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1310" t="n">
         <v>0</v>
@@ -27132,7 +27132,7 @@
         <v>1309</v>
       </c>
       <c r="B1311" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1311" t="n">
         <v>0</v>
@@ -27152,7 +27152,7 @@
         <v>1310</v>
       </c>
       <c r="B1312" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1312" t="n">
         <v>0</v>
@@ -27172,7 +27172,7 @@
         <v>1311</v>
       </c>
       <c r="B1313" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1313" t="n">
         <v>0</v>
@@ -27192,7 +27192,7 @@
         <v>1312</v>
       </c>
       <c r="B1314" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1314" t="n">
         <v>0</v>
@@ -27212,7 +27212,7 @@
         <v>1313</v>
       </c>
       <c r="B1315" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1315" t="n">
         <v>0</v>
@@ -27232,7 +27232,7 @@
         <v>1314</v>
       </c>
       <c r="B1316" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1316" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>1315</v>
       </c>
       <c r="B1317" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1317" t="n">
         <v>0</v>
@@ -27272,7 +27272,7 @@
         <v>1316</v>
       </c>
       <c r="B1318" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1318" t="n">
         <v>0</v>
@@ -27292,7 +27292,7 @@
         <v>1317</v>
       </c>
       <c r="B1319" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1319" t="n">
         <v>0</v>
@@ -27312,7 +27312,7 @@
         <v>1318</v>
       </c>
       <c r="B1320" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1320" t="n">
         <v>0</v>
@@ -27332,7 +27332,7 @@
         <v>1319</v>
       </c>
       <c r="B1321" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C1321" t="n">
         <v>0</v>
@@ -27652,7 +27652,7 @@
         <v>1335</v>
       </c>
       <c r="B1337" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1337" t="n">
         <v>0</v>
@@ -27672,7 +27672,7 @@
         <v>1336</v>
       </c>
       <c r="B1338" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1338" t="n">
         <v>0</v>
@@ -27692,7 +27692,7 @@
         <v>1337</v>
       </c>
       <c r="B1339" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1339" t="n">
         <v>0</v>
@@ -27712,7 +27712,7 @@
         <v>1338</v>
       </c>
       <c r="B1340" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1340" t="n">
         <v>0</v>
@@ -27732,7 +27732,7 @@
         <v>1339</v>
       </c>
       <c r="B1341" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1341" t="n">
         <v>0</v>
@@ -27752,7 +27752,7 @@
         <v>1340</v>
       </c>
       <c r="B1342" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1342" t="n">
         <v>0</v>
@@ -27772,7 +27772,7 @@
         <v>1341</v>
       </c>
       <c r="B1343" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1343" t="n">
         <v>0</v>
@@ -27792,7 +27792,7 @@
         <v>1342</v>
       </c>
       <c r="B1344" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1344" t="n">
         <v>0</v>
@@ -27812,7 +27812,7 @@
         <v>1343</v>
       </c>
       <c r="B1345" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1345" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>1344</v>
       </c>
       <c r="B1346" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1346" t="n">
         <v>0</v>
@@ -27852,7 +27852,7 @@
         <v>1345</v>
       </c>
       <c r="B1347" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1347" t="n">
         <v>0</v>
@@ -27872,7 +27872,7 @@
         <v>1346</v>
       </c>
       <c r="B1348" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1348" t="n">
         <v>0</v>
@@ -27892,7 +27892,7 @@
         <v>1347</v>
       </c>
       <c r="B1349" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1349" t="n">
         <v>0</v>
@@ -27912,7 +27912,7 @@
         <v>1348</v>
       </c>
       <c r="B1350" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1350" t="n">
         <v>0</v>
@@ -27932,7 +27932,7 @@
         <v>1349</v>
       </c>
       <c r="B1351" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1351" t="n">
         <v>0</v>
@@ -27952,7 +27952,7 @@
         <v>1350</v>
       </c>
       <c r="B1352" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1352" t="n">
         <v>0</v>
@@ -27972,7 +27972,7 @@
         <v>1351</v>
       </c>
       <c r="B1353" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1353" t="n">
         <v>0</v>
@@ -27992,7 +27992,7 @@
         <v>1352</v>
       </c>
       <c r="B1354" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1354" t="n">
         <v>0</v>
@@ -28012,7 +28012,7 @@
         <v>1353</v>
       </c>
       <c r="B1355" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1355" t="n">
         <v>0</v>
@@ -28032,7 +28032,7 @@
         <v>1354</v>
       </c>
       <c r="B1356" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1356" t="n">
         <v>0</v>
@@ -28052,7 +28052,7 @@
         <v>1355</v>
       </c>
       <c r="B1357" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1357" t="n">
         <v>0</v>
@@ -28072,7 +28072,7 @@
         <v>1356</v>
       </c>
       <c r="B1358" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1358" t="n">
         <v>0</v>
@@ -28092,7 +28092,7 @@
         <v>1357</v>
       </c>
       <c r="B1359" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1359" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
         <v>1358</v>
       </c>
       <c r="B1360" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1360" t="n">
         <v>0</v>
@@ -28132,7 +28132,7 @@
         <v>1359</v>
       </c>
       <c r="B1361" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1361" t="n">
         <v>0</v>
@@ -28152,7 +28152,7 @@
         <v>1360</v>
       </c>
       <c r="B1362" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1362" t="n">
         <v>0</v>
@@ -28172,7 +28172,7 @@
         <v>1361</v>
       </c>
       <c r="B1363" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1363" t="n">
         <v>0</v>
@@ -28192,7 +28192,7 @@
         <v>1362</v>
       </c>
       <c r="B1364" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1364" t="n">
         <v>0</v>
@@ -28212,7 +28212,7 @@
         <v>1363</v>
       </c>
       <c r="B1365" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1365" t="n">
         <v>0</v>
@@ -28232,7 +28232,7 @@
         <v>1364</v>
       </c>
       <c r="B1366" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1366" t="n">
         <v>0</v>
@@ -28252,7 +28252,7 @@
         <v>1365</v>
       </c>
       <c r="B1367" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1367" t="n">
         <v>0</v>
@@ -28272,7 +28272,7 @@
         <v>1366</v>
       </c>
       <c r="B1368" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1368" t="n">
         <v>0</v>
@@ -28292,7 +28292,7 @@
         <v>1367</v>
       </c>
       <c r="B1369" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1369" t="n">
         <v>0</v>
@@ -28312,7 +28312,7 @@
         <v>1368</v>
       </c>
       <c r="B1370" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1370" t="n">
         <v>0</v>
@@ -28332,7 +28332,7 @@
         <v>1369</v>
       </c>
       <c r="B1371" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1371" t="n">
         <v>0</v>
@@ -28352,7 +28352,7 @@
         <v>1370</v>
       </c>
       <c r="B1372" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1372" t="n">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>1371</v>
       </c>
       <c r="B1373" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1373" t="n">
         <v>0</v>
@@ -28392,7 +28392,7 @@
         <v>1372</v>
       </c>
       <c r="B1374" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1374" t="n">
         <v>0</v>
@@ -28412,7 +28412,7 @@
         <v>1373</v>
       </c>
       <c r="B1375" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1375" t="n">
         <v>0</v>
@@ -28432,7 +28432,7 @@
         <v>1374</v>
       </c>
       <c r="B1376" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1376" t="n">
         <v>0</v>
@@ -28452,7 +28452,7 @@
         <v>1375</v>
       </c>
       <c r="B1377" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1377" t="n">
         <v>0</v>
@@ -28472,7 +28472,7 @@
         <v>1376</v>
       </c>
       <c r="B1378" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1378" t="n">
         <v>0</v>
@@ -28492,7 +28492,7 @@
         <v>1377</v>
       </c>
       <c r="B1379" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1379" t="n">
         <v>0</v>
@@ -28512,7 +28512,7 @@
         <v>1378</v>
       </c>
       <c r="B1380" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1380" t="n">
         <v>0</v>
@@ -28532,7 +28532,7 @@
         <v>1379</v>
       </c>
       <c r="B1381" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1381" t="n">
         <v>0</v>
@@ -28552,7 +28552,7 @@
         <v>1380</v>
       </c>
       <c r="B1382" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1382" t="n">
         <v>0</v>
@@ -28572,7 +28572,7 @@
         <v>1381</v>
       </c>
       <c r="B1383" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1383" t="n">
         <v>0</v>
@@ -28592,7 +28592,7 @@
         <v>1382</v>
       </c>
       <c r="B1384" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1384" t="n">
         <v>0</v>
@@ -28612,7 +28612,7 @@
         <v>1383</v>
       </c>
       <c r="B1385" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1385" t="n">
         <v>0</v>
@@ -28632,7 +28632,7 @@
         <v>1384</v>
       </c>
       <c r="B1386" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1386" t="n">
         <v>0</v>
@@ -28652,7 +28652,7 @@
         <v>1385</v>
       </c>
       <c r="B1387" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1387" t="n">
         <v>0</v>
@@ -28672,7 +28672,7 @@
         <v>1386</v>
       </c>
       <c r="B1388" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1388" t="n">
         <v>0</v>
@@ -28692,7 +28692,7 @@
         <v>1387</v>
       </c>
       <c r="B1389" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1389" t="n">
         <v>0</v>
@@ -28712,7 +28712,7 @@
         <v>1388</v>
       </c>
       <c r="B1390" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1390" t="n">
         <v>0</v>
@@ -28732,7 +28732,7 @@
         <v>1389</v>
       </c>
       <c r="B1391" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1391" t="n">
         <v>0</v>
@@ -28752,7 +28752,7 @@
         <v>1390</v>
       </c>
       <c r="B1392" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1392" t="n">
         <v>0</v>
@@ -28772,7 +28772,7 @@
         <v>1391</v>
       </c>
       <c r="B1393" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1393" t="n">
         <v>0</v>
@@ -28792,7 +28792,7 @@
         <v>1392</v>
       </c>
       <c r="B1394" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1394" t="n">
         <v>0</v>
@@ -28812,7 +28812,7 @@
         <v>1393</v>
       </c>
       <c r="B1395" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1395" t="n">
         <v>0</v>
@@ -28832,7 +28832,7 @@
         <v>1394</v>
       </c>
       <c r="B1396" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1396" t="n">
         <v>0</v>
@@ -28852,7 +28852,7 @@
         <v>1395</v>
       </c>
       <c r="B1397" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1397" t="n">
         <v>0</v>
@@ -28872,7 +28872,7 @@
         <v>1396</v>
       </c>
       <c r="B1398" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1398" t="n">
         <v>0</v>
@@ -28892,7 +28892,7 @@
         <v>1397</v>
       </c>
       <c r="B1399" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1399" t="n">
         <v>0</v>
@@ -28912,7 +28912,7 @@
         <v>1398</v>
       </c>
       <c r="B1400" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1400" t="n">
         <v>0</v>
@@ -28932,7 +28932,7 @@
         <v>1399</v>
       </c>
       <c r="B1401" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1401" t="n">
         <v>0</v>
@@ -28952,7 +28952,7 @@
         <v>1400</v>
       </c>
       <c r="B1402" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1402" t="n">
         <v>0</v>
@@ -28972,7 +28972,7 @@
         <v>1401</v>
       </c>
       <c r="B1403" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1403" t="n">
         <v>0</v>
@@ -28992,7 +28992,7 @@
         <v>1402</v>
       </c>
       <c r="B1404" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1404" t="n">
         <v>0</v>
@@ -29012,7 +29012,7 @@
         <v>1403</v>
       </c>
       <c r="B1405" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1405" t="n">
         <v>0</v>
@@ -29032,7 +29032,7 @@
         <v>1404</v>
       </c>
       <c r="B1406" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1406" t="n">
         <v>0</v>
@@ -29052,7 +29052,7 @@
         <v>1405</v>
       </c>
       <c r="B1407" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1407" t="n">
         <v>0</v>
@@ -29072,7 +29072,7 @@
         <v>1406</v>
       </c>
       <c r="B1408" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1408" t="n">
         <v>0</v>
@@ -29092,7 +29092,7 @@
         <v>1407</v>
       </c>
       <c r="B1409" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1409" t="n">
         <v>0</v>
@@ -29112,7 +29112,7 @@
         <v>1408</v>
       </c>
       <c r="B1410" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1410" t="n">
         <v>0</v>
@@ -29132,7 +29132,7 @@
         <v>1409</v>
       </c>
       <c r="B1411" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1411" t="n">
         <v>0</v>
@@ -29152,7 +29152,7 @@
         <v>1410</v>
       </c>
       <c r="B1412" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1412" t="n">
         <v>0</v>
@@ -29172,7 +29172,7 @@
         <v>1411</v>
       </c>
       <c r="B1413" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1413" t="n">
         <v>0</v>
@@ -29192,7 +29192,7 @@
         <v>1412</v>
       </c>
       <c r="B1414" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1414" t="n">
         <v>0</v>
@@ -29212,7 +29212,7 @@
         <v>1413</v>
       </c>
       <c r="B1415" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1415" t="n">
         <v>0</v>
@@ -29232,7 +29232,7 @@
         <v>1414</v>
       </c>
       <c r="B1416" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1416" t="n">
         <v>0</v>
@@ -29252,7 +29252,7 @@
         <v>1415</v>
       </c>
       <c r="B1417" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1417" t="n">
         <v>0</v>
@@ -29272,7 +29272,7 @@
         <v>1416</v>
       </c>
       <c r="B1418" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1418" t="n">
         <v>0</v>
@@ -29292,7 +29292,7 @@
         <v>1417</v>
       </c>
       <c r="B1419" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1419" t="n">
         <v>0</v>
@@ -29312,7 +29312,7 @@
         <v>1418</v>
       </c>
       <c r="B1420" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1420" t="n">
         <v>0</v>
@@ -29332,7 +29332,7 @@
         <v>1419</v>
       </c>
       <c r="B1421" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1421" t="n">
         <v>0</v>
@@ -29352,7 +29352,7 @@
         <v>1420</v>
       </c>
       <c r="B1422" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1422" t="n">
         <v>0</v>
@@ -29372,7 +29372,7 @@
         <v>1421</v>
       </c>
       <c r="B1423" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1423" t="n">
         <v>0</v>
@@ -29392,7 +29392,7 @@
         <v>1422</v>
       </c>
       <c r="B1424" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1424" t="n">
         <v>0</v>
@@ -29412,7 +29412,7 @@
         <v>1423</v>
       </c>
       <c r="B1425" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1425" t="n">
         <v>0</v>
@@ -29432,7 +29432,7 @@
         <v>1424</v>
       </c>
       <c r="B1426" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1426" t="n">
         <v>0</v>
@@ -29452,7 +29452,7 @@
         <v>1425</v>
       </c>
       <c r="B1427" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1427" t="n">
         <v>0</v>
@@ -29472,7 +29472,7 @@
         <v>1426</v>
       </c>
       <c r="B1428" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1428" t="n">
         <v>0</v>
@@ -29492,7 +29492,7 @@
         <v>1427</v>
       </c>
       <c r="B1429" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1429" t="n">
         <v>0</v>
@@ -29512,7 +29512,7 @@
         <v>1428</v>
       </c>
       <c r="B1430" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1430" t="n">
         <v>0</v>
@@ -29532,7 +29532,7 @@
         <v>1429</v>
       </c>
       <c r="B1431" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1431" t="n">
         <v>0</v>
@@ -29552,7 +29552,7 @@
         <v>1430</v>
       </c>
       <c r="B1432" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1432" t="n">
         <v>0</v>
@@ -29572,7 +29572,7 @@
         <v>1431</v>
       </c>
       <c r="B1433" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1433" t="n">
         <v>0</v>
@@ -29592,7 +29592,7 @@
         <v>1432</v>
       </c>
       <c r="B1434" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1434" t="n">
         <v>0</v>
@@ -29612,7 +29612,7 @@
         <v>1433</v>
       </c>
       <c r="B1435" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1435" t="n">
         <v>0</v>
@@ -29632,7 +29632,7 @@
         <v>1434</v>
       </c>
       <c r="B1436" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1436" t="n">
         <v>0</v>
@@ -29652,7 +29652,7 @@
         <v>1435</v>
       </c>
       <c r="B1437" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1437" t="n">
         <v>0</v>
@@ -29672,7 +29672,7 @@
         <v>1436</v>
       </c>
       <c r="B1438" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1438" t="n">
         <v>0</v>
@@ -29692,7 +29692,7 @@
         <v>1437</v>
       </c>
       <c r="B1439" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1439" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
         <v>1438</v>
       </c>
       <c r="B1440" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C1440" t="n">
         <v>0</v>
@@ -29783,7 +29783,7 @@
         <v>46129</v>
       </c>
       <c r="B2" t="n">
-        <v>1062.038461538461</v>
+        <v>1378.25</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -29794,7 +29794,7 @@
         <v>46129.01041666666</v>
       </c>
       <c r="B3" t="n">
-        <v>1083.360465116279</v>
+        <v>1405.968604651163</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
@@ -29805,7 +29805,7 @@
         <v>46129.02083333334</v>
       </c>
       <c r="B4" t="n">
-        <v>1074.176686890973</v>
+        <v>1394.027652141938</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -29816,7 +29816,7 @@
         <v>46129.03125</v>
       </c>
       <c r="B5" t="n">
-        <v>1093.544771396931</v>
+        <v>1419.187794652745</v>
       </c>
       <c r="C5" t="n">
         <v>45</v>
@@ -29827,7 +29827,7 @@
         <v>46129.04166666666</v>
       </c>
       <c r="B6" t="n">
-        <v>996.4289582669642</v>
+        <v>1292.937097801848</v>
       </c>
       <c r="C6" t="n">
         <v>60</v>
@@ -29838,7 +29838,7 @@
         <v>46129.05208333334</v>
       </c>
       <c r="B7" t="n">
-        <v>1006.175572519084</v>
+        <v>1305.628244274809</v>
       </c>
       <c r="C7" t="n">
         <v>75</v>
@@ -29849,7 +29849,7 @@
         <v>46129.0625</v>
       </c>
       <c r="B8" t="n">
-        <v>1054.913698630137</v>
+        <v>1368.983698630137</v>
       </c>
       <c r="C8" t="n">
         <v>90</v>
@@ -29860,7 +29860,7 @@
         <v>46129.07291666666</v>
       </c>
       <c r="B9" t="n">
-        <v>1067.473469387755</v>
+        <v>1385.313469387755</v>
       </c>
       <c r="C9" t="n">
         <v>105</v>
@@ -29871,7 +29871,7 @@
         <v>46129.08333333334</v>
       </c>
       <c r="B10" t="n">
-        <v>1078.309174896464</v>
+        <v>1399.399872570883</v>
       </c>
       <c r="C10" t="n">
         <v>120</v>
@@ -29882,7 +29882,7 @@
         <v>46129.09375</v>
       </c>
       <c r="B11" t="n">
-        <v>1100.558139534884</v>
+        <v>1428.325581395349</v>
       </c>
       <c r="C11" t="n">
         <v>135</v>
@@ -29893,7 +29893,7 @@
         <v>46129.10416666666</v>
       </c>
       <c r="B12" t="n">
-        <v>1101.431818181818</v>
+        <v>1429.461363636364</v>
       </c>
       <c r="C12" t="n">
         <v>150</v>
@@ -29904,7 +29904,7 @@
         <v>46129.11458333334</v>
       </c>
       <c r="B13" t="n">
-        <v>1102.087983532896</v>
+        <v>1430.312337776439</v>
       </c>
       <c r="C13" t="n">
         <v>165</v>
@@ -29915,7 +29915,7 @@
         <v>46129.125</v>
       </c>
       <c r="B14" t="n">
-        <v>1095.988764044944</v>
+        <v>1422.385393258427</v>
       </c>
       <c r="C14" t="n">
         <v>180</v>
@@ -29926,7 +29926,7 @@
         <v>46129.13541666666</v>
       </c>
       <c r="B15" t="n">
-        <v>1099.362934362934</v>
+        <v>1426.771814671815</v>
       </c>
       <c r="C15" t="n">
         <v>195</v>
@@ -29937,7 +29937,7 @@
         <v>46129.14583333334</v>
       </c>
       <c r="B16" t="n">
-        <v>1066.169640012743</v>
+        <v>1383.618477222045</v>
       </c>
       <c r="C16" t="n">
         <v>210</v>
@@ -29948,7 +29948,7 @@
         <v>46129.15625</v>
       </c>
       <c r="B17" t="n">
-        <v>1061.825635517365</v>
+        <v>1377.969244539921</v>
       </c>
       <c r="C17" t="n">
         <v>225</v>
@@ -29959,7 +29959,7 @@
         <v>46129.16666666666</v>
       </c>
       <c r="B18" t="n">
-        <v>1061.680365296804</v>
+        <v>1377.780365296804</v>
       </c>
       <c r="C18" t="n">
         <v>240</v>
@@ -29970,7 +29970,7 @@
         <v>46129.17708333334</v>
       </c>
       <c r="B19" t="n">
-        <v>1085.708487084871</v>
+        <v>1409.021033210332</v>
       </c>
       <c r="C19" t="n">
         <v>255</v>
@@ -29981,7 +29981,7 @@
         <v>46129.1875</v>
       </c>
       <c r="B20" t="n">
-        <v>1078.315184282668</v>
+        <v>1399.403617118489</v>
       </c>
       <c r="C20" t="n">
         <v>270</v>
@@ -29992,7 +29992,7 @@
         <v>46129.19791666666</v>
       </c>
       <c r="B21" t="n">
-        <v>1093.386585681055</v>
+        <v>1418.996397001809</v>
       </c>
       <c r="C21" t="n">
         <v>285</v>
@@ -30003,7 +30003,7 @@
         <v>46129.20833333334</v>
       </c>
       <c r="B22" t="n">
-        <v>1074.831897778123</v>
+        <v>1394.879426295233</v>
       </c>
       <c r="C22" t="n">
         <v>300</v>
@@ -30014,7 +30014,7 @@
         <v>46129.21875</v>
       </c>
       <c r="B23" t="n">
-        <v>1070.366666666667</v>
+        <v>1389.076666666667</v>
       </c>
       <c r="C23" t="n">
         <v>315</v>
@@ -30025,7 +30025,7 @@
         <v>46129.22916666666</v>
       </c>
       <c r="B24" t="n">
-        <v>1053.031592781681</v>
+        <v>1366.52052267098</v>
       </c>
       <c r="C24" t="n">
         <v>330</v>
@@ -30036,7 +30036,7 @@
         <v>46129.23958333334</v>
       </c>
       <c r="B25" t="n">
-        <v>1251.903022277613</v>
+        <v>1603.057602430285</v>
       </c>
       <c r="C25" t="n">
         <v>345</v>
@@ -30047,7 +30047,7 @@
         <v>46129.25</v>
       </c>
       <c r="B26" t="n">
-        <v>1182.027397260274</v>
+        <v>1506.927397260274</v>
       </c>
       <c r="C26" t="n">
         <v>360</v>
@@ -30058,7 +30058,7 @@
         <v>46129.26041666666</v>
       </c>
       <c r="B27" t="n">
-        <v>1161.734219269103</v>
+        <v>1479.183056478405</v>
       </c>
       <c r="C27" t="n">
         <v>375</v>
@@ -30069,7 +30069,7 @@
         <v>46129.27083333334</v>
       </c>
       <c r="B28" t="n">
-        <v>1152.948936623847</v>
+        <v>1466.758275145248</v>
       </c>
       <c r="C28" t="n">
         <v>390</v>
@@ -30080,7 +30080,7 @@
         <v>46129.28125</v>
       </c>
       <c r="B29" t="n">
-        <v>1148.670711527854</v>
+        <v>1460.963761720905</v>
       </c>
       <c r="C29" t="n">
         <v>405</v>
@@ -30091,7 +30091,7 @@
         <v>46129.29166666666</v>
       </c>
       <c r="B30" t="n">
-        <v>1148.830858413404</v>
+        <v>1461.116850631303</v>
       </c>
       <c r="C30" t="n">
         <v>420</v>
@@ -30102,7 +30102,7 @@
         <v>46129.30208333334</v>
       </c>
       <c r="B31" t="n">
-        <v>1148.122448979592</v>
+        <v>1461.322448979592</v>
       </c>
       <c r="C31" t="n">
         <v>435</v>
@@ -30113,7 +30113,7 @@
         <v>46129.3125</v>
       </c>
       <c r="B32" t="n">
-        <v>1145.321917808219</v>
+        <v>1458.521917808219</v>
       </c>
       <c r="C32" t="n">
         <v>450</v>
@@ -30124,7 +30124,7 @@
         <v>46129.32291666666</v>
       </c>
       <c r="B33" t="n">
-        <v>1141.9640276344</v>
+        <v>1454.8593583737</v>
       </c>
       <c r="C33" t="n">
         <v>465</v>
@@ -30663,7 +30663,7 @@
         <v>46129.83333333334</v>
       </c>
       <c r="B82" t="n">
-        <v>1607.458806578122</v>
+        <v>1930.975755730665</v>
       </c>
       <c r="C82" t="n">
         <v>1200</v>
@@ -30674,7 +30674,7 @@
         <v>46129.84375</v>
       </c>
       <c r="B83" t="n">
-        <v>1757.303797468354</v>
+        <v>2425.025316455696</v>
       </c>
       <c r="C83" t="n">
         <v>1215</v>
@@ -30685,7 +30685,7 @@
         <v>46129.85416666666</v>
       </c>
       <c r="B84" t="n">
-        <v>1728.818493150685</v>
+        <v>2366.318493150685</v>
       </c>
       <c r="C84" t="n">
         <v>1230</v>
@@ -30696,7 +30696,7 @@
         <v>46129.86458333334</v>
       </c>
       <c r="B85" t="n">
-        <v>1331.041591320072</v>
+        <v>1791.801084990958</v>
       </c>
       <c r="C85" t="n">
         <v>1245</v>
@@ -30707,7 +30707,7 @@
         <v>46129.875</v>
       </c>
       <c r="B86" t="n">
-        <v>144.4459857811687</v>
+        <v>150.1421883128143</v>
       </c>
       <c r="C86" t="n">
         <v>1260</v>
@@ -30718,7 +30718,7 @@
         <v>46129.88541666666</v>
       </c>
       <c r="B87" t="n">
-        <v>1142.972544694683</v>
+        <v>1143.608137915022</v>
       </c>
       <c r="C87" t="n">
         <v>1275</v>
@@ -30729,7 +30729,7 @@
         <v>46129.89583333334</v>
       </c>
       <c r="B88" t="n">
-        <v>2677.732876712329</v>
+        <v>3247.732876712329</v>
       </c>
       <c r="C88" t="n">
         <v>1290</v>
@@ -30740,7 +30740,7 @@
         <v>46129.90625</v>
       </c>
       <c r="B89" t="n">
-        <v>1362.659863945578</v>
+        <v>1680.659863945578</v>
       </c>
       <c r="C89" t="n">
         <v>1305</v>
@@ -30751,7 +30751,7 @@
         <v>46129.91666666666</v>
       </c>
       <c r="B90" t="n">
-        <v>1548.994155251142</v>
+        <v>2064.994155251141</v>
       </c>
       <c r="C90" t="n">
         <v>1320</v>
@@ -30773,7 +30773,7 @@
         <v>46129.9375</v>
       </c>
       <c r="B92" t="n">
-        <v>1190.906822906823</v>
+        <v>1562.906822906823</v>
       </c>
       <c r="C92" t="n">
         <v>1350</v>
@@ -30784,7 +30784,7 @@
         <v>46129.94791666666</v>
       </c>
       <c r="B93" t="n">
-        <v>1336.837004813032</v>
+        <v>1762.837004813032</v>
       </c>
       <c r="C93" t="n">
         <v>1365</v>
@@ -30795,7 +30795,7 @@
         <v>46129.95833333334</v>
       </c>
       <c r="B94" t="n">
-        <v>1202.965753424658</v>
+        <v>1640.965753424658</v>
       </c>
       <c r="C94" t="n">
         <v>1380</v>
@@ -30806,7 +30806,7 @@
         <v>46129.96875</v>
       </c>
       <c r="B95" t="n">
-        <v>1097.109589041096</v>
+        <v>1493.109589041096</v>
       </c>
       <c r="C95" t="n">
         <v>1395</v>
@@ -30817,7 +30817,7 @@
         <v>46129.97916666666</v>
       </c>
       <c r="B96" t="n">
-        <v>457.1613052000461</v>
+        <v>596.9918136746223</v>
       </c>
       <c r="C96" t="n">
         <v>1410</v>
@@ -30828,7 +30828,7 @@
         <v>46129.98958333334</v>
       </c>
       <c r="B97" t="n">
-        <v>872.228617474387</v>
+        <v>1177.90088638195</v>
       </c>
       <c r="C97" t="n">
         <v>1425</v>
@@ -30885,7 +30885,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1060.368218015183</v>
+        <v>1378.478683419738</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -30929,7 +30929,7 @@
         <v>464</v>
       </c>
       <c r="B4" t="n">
-        <v>-1060.368218015183</v>
+        <v>-1378.478683419738</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -30940,7 +30940,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8.20018088598408</v>
+        <v>10.66023515177931</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -31017,7 +31017,7 @@
         <v>1185</v>
       </c>
       <c r="B8" t="n">
-        <v>1305.936226131731</v>
+        <v>1828.310716584424</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -31083,7 +31083,7 @@
         <v>1245</v>
       </c>
       <c r="B11" t="n">
-        <v>-1305.936226131731</v>
+        <v>-1828.310716584424</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -31094,7 +31094,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.305936226131731</v>
+        <v>1.828310716584424</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -31171,7 +31171,7 @@
         <v>1275</v>
       </c>
       <c r="B15" t="n">
-        <v>1170</v>
+        <v>1638</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -31215,7 +31215,7 @@
         <v>1320</v>
       </c>
       <c r="B17" t="n">
-        <v>-1170</v>
+        <v>-1638</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -31226,7 +31226,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8774999999999999</v>
+        <v>1.2285</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -31237,7 +31237,7 @@
         <v>1335</v>
       </c>
       <c r="B18" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -31281,7 +31281,7 @@
         <v>1439</v>
       </c>
       <c r="B20" t="n">
-        <v>-782.1509253948951</v>
+        <v>-1278.953957287405</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -31292,7 +31292,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.355728270684485</v>
+        <v>2.216853525964835</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
